--- a/Quotation_Template.xlsx
+++ b/Quotation_Template.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">[Your Address]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quote No:</t>
+    <t xml:space="preserve">QUOTE NO.</t>
   </si>
   <si>
     <t xml:space="preserve">QUO-0001</t>
@@ -40,19 +40,19 @@
     <t xml:space="preserve">[City, Postal Code]</t>
   </si>
   <si>
-    <t xml:space="preserve">Date:</t>
+    <t xml:space="preserve">DATE</t>
   </si>
   <si>
     <t xml:space="preserve">[DD/MM/YYYY]</t>
   </si>
   <si>
-    <t xml:space="preserve">[Phone Number]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid Until:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Email Address]</t>
+    <t xml:space="preserve">[Phone]  •  [Email]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALID UNTIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAT No: [if registered]</t>
   </si>
   <si>
     <t xml:space="preserve">  PREPARED FOR</t>
@@ -73,10 +73,10 @@
     <t xml:space="preserve">QTY</t>
   </si>
   <si>
-    <t xml:space="preserve">UNIT PRICE (R)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMOUNT (R)</t>
+    <t xml:space="preserve">UNIT PRICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMOUNT</t>
   </si>
   <si>
     <t xml:space="preserve">Subtotal</t>
@@ -91,16 +91,16 @@
     <t xml:space="preserve">  TERMS &amp; CONDITIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">• This quotation is valid until the date shown above.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Prices include VAT unless stated otherwise.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• 50% deposit may be required to begin work.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• [Add your own terms here]</t>
+    <t xml:space="preserve">•  This quotation is valid until the date shown above.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Prices include VAT unless stated otherwise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  A 50% deposit may be required to begin work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  [Add your own terms here]</t>
   </si>
 </sst>
 </file>
@@ -112,7 +112,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,90 +137,75 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="22"/>
-      <color rgb="FF2563EB"/>
-      <name val="Arial"/>
+      <sz val="20"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="28"/>
-      <color rgb="FF1E293B"/>
-      <name val="Arial"/>
+      <color rgb="FF2563EB"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF64748B"/>
-      <name val="Arial"/>
+      <color rgb="FF475569"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FF94A3B8"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1E293B"/>
-      <name val="Arial"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <color rgb="FF475569"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1E293B"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FF1E293B"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,14 +214,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="FF2563EB"/>
+        <bgColor rgb="FF0066CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2563EB"/>
-        <bgColor rgb="FF0066CC"/>
+        <fgColor rgb="FF0F172A"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -250,16 +247,16 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFE2E8F0"/>
       </left>
       <right style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFE2E8F0"/>
       </right>
       <top style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFE2E8F0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFE2E8F0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -289,11 +286,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -314,52 +315,80 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -391,12 +420,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF1F5F9"/>
+      <rgbColor rgb="FFE2E8F0"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCBD5E1"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -419,16 +448,16 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF64748B"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF475569"/>
+      <rgbColor rgb="FF94A3B8"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF0F172A"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1E293B"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -614,275 +643,282 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F35"/>
+  <dimension ref="B1:F36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="2.5"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="33.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="33.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="2" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8" t="s">
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="9" t="s">
+      <c r="E15" s="12"/>
+      <c r="F15" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13" t="str">
-        <f aca="false">IF(AND(C15&lt;&gt;"",D15&lt;&gt;""),C15*D15,"")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13" t="str">
+      <c r="B16" s="14"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="17" t="str">
         <f aca="false">IF(AND(C16&lt;&gt;"",D16&lt;&gt;""),C16*D16,"")</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13" t="str">
+      <c r="B17" s="18"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="21" t="str">
         <f aca="false">IF(AND(C17&lt;&gt;"",D17&lt;&gt;""),C17*D17,"")</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13" t="str">
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="17" t="str">
         <f aca="false">IF(AND(C18&lt;&gt;"",D18&lt;&gt;""),C18*D18,"")</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13" t="str">
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="21" t="str">
         <f aca="false">IF(AND(C19&lt;&gt;"",D19&lt;&gt;""),C19*D19,"")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13" t="str">
+      <c r="B20" s="14"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="17" t="str">
         <f aca="false">IF(AND(C20&lt;&gt;"",D20&lt;&gt;""),C20*D20,"")</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13" t="str">
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="21" t="str">
         <f aca="false">IF(AND(C21&lt;&gt;"",D21&lt;&gt;""),C21*D21,"")</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13" t="str">
+      <c r="B22" s="14"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="17" t="str">
         <f aca="false">IF(AND(C22&lt;&gt;"",D22&lt;&gt;""),C22*D22,"")</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13" t="str">
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="21" t="str">
         <f aca="false">IF(AND(C23&lt;&gt;"",D23&lt;&gt;""),C23*D23,"")</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13" t="str">
+      <c r="B24" s="14"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="17" t="str">
         <f aca="false">IF(AND(C24&lt;&gt;"",D24&lt;&gt;""),C24*D24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="14" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="21" t="str">
+        <f aca="false">IF(AND(C25&lt;&gt;"",D25&lt;&gt;""),C25*D25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D27" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="15" t="n">
-        <f aca="false">SUM(F15:F24)</f>
+      <c r="E27" s="22"/>
+      <c r="F27" s="23" t="n">
+        <f aca="false">SUM(F16:F25)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="14" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="14"/>
-      <c r="F27" s="15" t="n">
-        <f aca="false">F26*0.15</f>
+      <c r="E28" s="22"/>
+      <c r="F28" s="23" t="n">
+        <f aca="false">F27*0.15</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="16" t="s">
+    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D29" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="17" t="n">
-        <f aca="false">F26+F27</f>
+      <c r="E29" s="24"/>
+      <c r="F29" s="25" t="n">
+        <f aca="false">F27+F28</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="6" t="s">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="3" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="3" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="3" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="4" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="B10:F10"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="D17:E17"/>
@@ -893,10 +929,11 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D25:E25"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
